--- a/public/exports-60-250-with-coowners/29189560.xlsx
+++ b/public/exports-60-250-with-coowners/29189560.xlsx
@@ -10714,7 +10714,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
